--- a/ProjectDescription/DownloadAdapter_FunctionNameReg.xlsx
+++ b/ProjectDescription/DownloadAdapter_FunctionNameReg.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1125,6 +1125,132 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>setSpeedSizeText</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>task&lt;DownloadTask&gt;</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>设置下载速度和已下载/总大小文本显示，速度&gt;0时显示"⬇ 速度 · 已下载/总大小"</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadAdapter.java)[DownloadAdapter.ViewHolder-&gt;setSpeedSizeText:234]</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>下载中和暂停状态均显示，数据不足时隐藏</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>formatSpeedStatic</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>bytesPerSec&lt;double&gt;</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>将字节/秒格式化为可读速度文本（如"2.3 MiB/s"），静态方法</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadAdapter.java)[DownloadAdapter.ViewHolder-&gt;formatSpeedStatic:259]</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>支持B/s、KiB/s、MiB/s三级单位</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>formatBytesStatic</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>bytes&lt;long&gt;</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>将字节数格式化为可读大小文本（如"45.2 MB"），静态方法</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadAdapter.java)[DownloadAdapter.ViewHolder-&gt;formatBytesStatic:272]</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>支持B、KB、MB三级单位</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ProjectDescription/DownloadAdapter_FunctionNameReg.xlsx
+++ b/ProjectDescription/DownloadAdapter_FunctionNameReg.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,7 +528,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadAdapter.java)[OnTaskActionListener:37]</t>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadAdapter.java)[OnTaskActionListener:32]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1248,6 +1248,48 @@
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t>支持B、KB、MB三级单位</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>onShare</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>task&lt;DownloadTask&gt;</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>分享操作回调（接口抽象方法），将已下载的文件通过系统分享发送给其他应用</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadAdapter.java)[OnTaskActionListener-&gt;onShare:43]</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026年06月20日23时55分23秒</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>由DownloadFragment实现</t>
         </is>
       </c>
     </row>
